--- a/06_Statistics/Assignment/Statistics_Data_Analytics_Assignment/Statistics_Data_Analytics_Working.xlsx
+++ b/06_Statistics/Assignment/Statistics_Data_Analytics_Assignment/Statistics_Data_Analytics_Working.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data_Analytics_Karthick_V\06_Statistics\Assignment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data_Analytics_Karthick_V\06_Statistics\Assignment\Statistics_Data_Analytics_Assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4D931D-3F20-4100-9699-FD1CC89F3075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48C9776-1F4E-438D-AF2B-4510F079B3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,9 @@
     <sheet name="Dataset" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Dataset!$D$2:$D$51</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Dataset!$D$1</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Dataset!$D$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Dataset!$D$2:$D$51</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Dataset!$D$2:$D$51</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Dataset!$D$2:$D$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="109">
   <si>
     <t>Information</t>
   </si>
@@ -349,12 +348,33 @@
   </si>
   <si>
     <t>AFTER OUTLIER EXCLUDE=</t>
+  </si>
+  <si>
+    <t>KURTOSIS=</t>
+  </si>
+  <si>
+    <t>randomly selected customer</t>
+  </si>
+  <si>
+    <t>discount greater than 20%</t>
+  </si>
+  <si>
+    <t>more than 5 days to deliver</t>
+  </si>
+  <si>
+    <t>epeat Customer probability</t>
+  </si>
+  <si>
+    <t>overall probability</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -404,12 +424,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,7 +453,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -468,7 +489,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{00000000-6EE2-4653-9563-1E3B1A6C41B0}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Order_Value</cx:v>
             </cx:txData>
           </cx:tx>
@@ -497,7 +518,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1698,7 +1719,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5875734" y="10945415"/>
+              <a:off x="5887640" y="10945415"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1776,7 +1797,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5810251" y="13898167"/>
+              <a:off x="5822157" y="13898167"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2230,7 +2251,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -4328,6 +4349,60 @@
         <v>5683.695652173913</v>
       </c>
     </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85" s="3">
+        <f>KURT(D2:D51)</f>
+        <v>6.3928020483431194</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>104</v>
+      </c>
+      <c r="D87">
+        <f>COUNTIF(J2:J51,"Yes")/COUNTA(J2:J51)</f>
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89">
+        <f>COUNTIF(F2:F51,"&gt;20")/COUNT(F2:F51)</f>
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>106</v>
+      </c>
+      <c r="D91">
+        <f>COUNTIF(G2:G51,"&gt;5")/COUNT(G2:G51)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>107</v>
+      </c>
+      <c r="D93" s="2">
+        <f>COUNTIFS(D2:D51,"&gt;5000",J2:J51,"Yes")/COUNTIF(D2:D51,"&gt;5000")*100</f>
+        <v>46.428571428571431</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>108</v>
+      </c>
+      <c r="D95">
+        <f>COUNTIF(J2:J51,"Yes")/COUNTA(J2:J51)*100</f>
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
